--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486684_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486684_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.697800000000001</v>
+        <v>9.104699999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8644</v>
+        <v>8.023</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8334</v>
+        <v>1.0817</v>
       </c>
       <c r="G2" t="n">
         <v>6.7497</v>
@@ -610,13 +610,13 @@
         <v>2.51</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.986</v>
+        <v>-1.579</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0485</v>
+        <v>-0.8899</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9375</v>
+        <v>-0.6892</v>
       </c>
       <c r="V2" t="n">
         <v>3.3548</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.652</v>
+        <v>2.0384</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7068</v>
+        <v>3.0932</v>
       </c>
       <c r="F3" t="n">
         <v>-1.0548</v>
@@ -688,10 +688,10 @@
         <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1859</v>
+        <v>0.5723</v>
       </c>
       <c r="T3" t="n">
-        <v>0.772</v>
+        <v>0.1584</v>
       </c>
       <c r="U3" t="n">
         <v>0.4139</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2524</v>
+        <v>0.5945</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0779</v>
+        <v>1.3952</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8255</v>
+        <v>-0.8007</v>
       </c>
       <c r="G4" t="n">
         <v>-0.6192</v>
@@ -766,13 +766,13 @@
         <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.48</v>
+        <v>-0.1379</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5518</v>
+        <v>-0.2346</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7624</v>
+        <v>-0.7225</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.5004</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0482</v>
+        <v>-0.222</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4359</v>
@@ -844,13 +844,13 @@
         <v>2.3169</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.9637</v>
+        <v>-1.9237</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4899</v>
+        <v>-1.2761</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4738</v>
+        <v>-0.6476</v>
       </c>
       <c r="V5" t="n">
         <v>0.2856</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.6343</v>
+        <v>-1.2633</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2018</v>
+        <v>1.6224</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.8361</v>
+        <v>-2.8857</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6551</v>
@@ -922,13 +922,13 @@
         <v>2.51</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.5431</v>
+        <v>-2.1722</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.6003</v>
+        <v>-1.1797</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9428</v>
+        <v>-0.9925</v>
       </c>
       <c r="V6" t="n">
         <v>0.9847</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7889</v>
+        <v>-1.684</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6632</v>
+        <v>-1.608</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1257</v>
+        <v>-0.076</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1324</v>
@@ -1000,13 +1000,13 @@
         <v>0.3862</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.0276</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1104</v>
+        <v>-0.0552</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0331</v>
+        <v>0.0828</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. DEL CASTILLO LEON</t>
+          <t>N. LUIS HERRERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6304</v>
+        <v>-2.6802</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7765</v>
+        <v>-0.3141</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1461</v>
+        <v>-2.3661</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5362</v>
+        <v>-0.6181</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1248</v>
+        <v>-1.6829</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4114</v>
+        <v>1.0648</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4345</v>
+        <v>0.8168</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7811</v>
+        <v>-0.6481</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6534</v>
+        <v>1.4649</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8983</v>
+        <v>-1.4349</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6563</v>
+        <v>-1.0348</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.242</v>
+        <v>-0.4002</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.8616</v>
+        <v>-0.9654</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7031</v>
+        <v>0.7723</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1087</v>
+        <v>-0.0275</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0212</v>
+        <v>-0.1655</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.08749999999999999</v>
+        <v>0.138</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8995</v>
+        <v>-1.8415</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3282</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5712</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. LUIS HERRERA</t>
+          <t>J. DEL CASTILLO LEON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7354</v>
+        <v>-3.1491</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3693</v>
+        <v>-2.873</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3661</v>
+        <v>-0.2761</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6181</v>
+        <v>0.5362</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6829</v>
+        <v>0.1248</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0648</v>
+        <v>0.4114</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8168</v>
+        <v>2.4345</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6481</v>
+        <v>1.7811</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4649</v>
+        <v>0.6534</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4349</v>
+        <v>-1.8983</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0348</v>
+        <v>-1.6563</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4002</v>
+        <v>-0.242</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7723</v>
+        <v>2.7031</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0827</v>
+        <v>-1.6273</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2207</v>
+        <v>-1.1176</v>
       </c>
       <c r="U9" t="n">
-        <v>0.138</v>
+        <v>-0.5097</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8415</v>
+        <v>-0.8995</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3282</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8415</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7828</v>
+        <v>-4.6587</v>
       </c>
       <c r="E10" t="n">
         <v>-2.6826</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1003</v>
+        <v>-1.9761</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1522</v>
@@ -1234,13 +1234,13 @@
         <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8551</v>
+        <v>-0.7309</v>
       </c>
       <c r="T10" t="n">
         <v>-0.6622</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1929</v>
+        <v>-0.0687</v>
       </c>
       <c r="V10" t="n">
         <v>-2.741</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.8512</v>
+        <v>-6.3353</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.0099</v>
+        <v>-5.6927</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8413</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-3.5633</v>
@@ -1312,13 +1312,13 @@
         <v>2.3169</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.7087</v>
+        <v>-2.1928</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3796</v>
+        <v>-1.0623</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3291</v>
+        <v>-1.1305</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.583199999999998</v>
+        <v>-8.7555</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3647999999999998</v>
+        <v>0.4630000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.218499999999999</v>
+        <v>-9.218399999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-0.1040000000000005</v>
@@ -1390,13 +1390,13 @@
         <v>17.3769</v>
       </c>
       <c r="S12" t="n">
-        <v>-10.6194</v>
+        <v>-9.791399999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-7.312600000000001</v>
+        <v>-6.4847</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.3067</v>
+        <v>-3.3068</v>
       </c>
       <c r="V12" t="n">
         <v>-1.756399999999999</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. GANDARA MARTIN</t>
+          <t>J. GARCIA CABRERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,40 +1423,40 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4913</v>
+        <v>4.9682</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9198</v>
+        <v>3.3418</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5715</v>
+        <v>1.6264</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8070000000000001</v>
+        <v>4.3617</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4971</v>
+        <v>1.1719</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.6902</v>
+        <v>3.1898</v>
       </c>
       <c r="J13" t="n">
-        <v>1.47</v>
+        <v>3.7283</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1872</v>
+        <v>1.2415</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.7172</v>
+        <v>2.4868</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.663</v>
+        <v>0.6334</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6901</v>
+        <v>-0.0697</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0271</v>
+        <v>0.703</v>
       </c>
       <c r="P13" t="n">
         <v>0.5792</v>
@@ -1468,28 +1468,28 @@
         <v>1.5446</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3061</v>
+        <v>1.255</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7168</v>
+        <v>0.5789</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5894</v>
+        <v>0.6761</v>
       </c>
       <c r="V13" t="n">
-        <v>1.7989</v>
+        <v>-1.2277</v>
       </c>
       <c r="W13" t="n">
-        <v>2.6984</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8995</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. GARCIA CABRERA</t>
+          <t>E. GANDARA MARTIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3238</v>
+        <v>4.8953</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1692</v>
+        <v>3.9198</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1546</v>
+        <v>0.9755</v>
       </c>
       <c r="G14" t="n">
-        <v>4.3617</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1719</v>
+        <v>3.4971</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1898</v>
+        <v>-2.6902</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7283</v>
+        <v>1.47</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2415</v>
+        <v>4.1872</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4868</v>
+        <v>-2.7172</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6334</v>
+        <v>-0.663</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0697</v>
+        <v>-0.6901</v>
       </c>
       <c r="O14" t="n">
-        <v>0.703</v>
+        <v>0.0271</v>
       </c>
       <c r="P14" t="n">
         <v>0.5792</v>
@@ -1546,28 +1546,28 @@
         <v>1.5446</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6105</v>
+        <v>1.7102</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4063</v>
+        <v>0.7168</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2043</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2277</v>
+        <v>1.7989</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.6984</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2277</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. MOLINA HERRERA</t>
+          <t>J. GONZÁLEZ CHÁVEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9851</v>
+        <v>4.7158</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7963</v>
+        <v>3.1953</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1888</v>
+        <v>1.5206</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.528</v>
+        <v>3.6289</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1382</v>
+        <v>1.635</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.6662</v>
+        <v>1.9939</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3425</v>
+        <v>4.3676</v>
       </c>
       <c r="K15" t="n">
-        <v>0.139</v>
+        <v>1.8424</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2035</v>
+        <v>2.5252</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8704</v>
+        <v>-0.7387</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0008</v>
+        <v>-0.2074</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8697</v>
+        <v>-0.5313</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7723</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7031</v>
+        <v>1.3515</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7142</v>
+        <v>0.7241</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1303</v>
+        <v>0.1446</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5838</v>
+        <v>0.5795</v>
       </c>
       <c r="V15" t="n">
-        <v>3.0266</v>
+        <v>0.9421</v>
       </c>
       <c r="W15" t="n">
-        <v>4.2543</v>
+        <v>0.6138</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2277</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. GONZÁLEZ CHÁVEZ</t>
+          <t>M. MOLINA HERRERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.7199</v>
+        <v>4.5051</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2987</v>
+        <v>3.5895</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4212</v>
+        <v>0.9157</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6289</v>
+        <v>-1.528</v>
       </c>
       <c r="H16" t="n">
-        <v>1.635</v>
+        <v>0.1382</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9939</v>
+        <v>-1.6662</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3676</v>
+        <v>0.3425</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8424</v>
+        <v>0.139</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5252</v>
+        <v>0.2035</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7387</v>
+        <v>-1.8704</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2074</v>
+        <v>-0.0008</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5313</v>
+        <v>-1.8697</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3515</v>
+        <v>2.7031</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7282</v>
+        <v>2.2342</v>
       </c>
       <c r="T16" t="n">
-        <v>0.248</v>
+        <v>0.9235</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4801</v>
+        <v>1.3107</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9421</v>
+        <v>3.0266</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6138</v>
+        <v>4.2543</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3282</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7793</v>
+        <v>2.4247</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0496</v>
+        <v>2.6702</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2703</v>
+        <v>-0.2455</v>
       </c>
       <c r="G17" t="n">
         <v>3.1175</v>
@@ -1780,13 +1780,13 @@
         <v>1.9308</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1764</v>
+        <v>0.469</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7725</v>
+        <v>-0.152</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5961</v>
+        <v>0.621</v>
       </c>
       <c r="V17" t="n">
         <v>-2.1271</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7254</v>
+        <v>0.9033</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2898</v>
+        <v>1.3932</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5643</v>
+        <v>-0.4898</v>
       </c>
       <c r="G18" t="n">
         <v>0.0619</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0497</v>
+        <v>0.2276</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.1034</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0497</v>
+        <v>0.1242</v>
       </c>
       <c r="V18" t="n">
         <v>0.6138</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. OMERAGIC ALIC</t>
+          <t>E. GONZALEZ CAMEJO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0961</v>
+        <v>0.1137</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4897</v>
+        <v>-0.5883</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5859</v>
+        <v>0.702</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0618</v>
+        <v>-2.0506</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4898</v>
+        <v>-2.6677</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5516</v>
+        <v>0.6171</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0621</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0621</v>
+        <v>-1.7705</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.266</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0003</v>
+        <v>-1.5461</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.8972</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5516</v>
+        <v>-0.6489</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7723</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1931</v>
+        <v>2.7031</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0923</v>
+        <v>1.5238</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4136</v>
+        <v>0.7511</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6787</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2856</v>
+        <v>1.7989</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.0266</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. GONZALEZ CAMEJO</t>
+          <t>A. OMERAGIC ALIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3953</v>
+        <v>-0.541</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8986</v>
+        <v>-0.9034</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5033</v>
+        <v>0.3624</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0506</v>
+        <v>0.0618</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.6677</v>
+        <v>-0.4898</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6171</v>
+        <v>0.5516</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5044999999999999</v>
+        <v>0.0621</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.7705</v>
+        <v>0.0621</v>
       </c>
       <c r="L20" t="n">
-        <v>1.266</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5461</v>
+        <v>-0.0003</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8972</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6489</v>
+        <v>0.5516</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1585</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.8616</v>
+        <v>-0.9654</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7031</v>
+        <v>0.1931</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0149</v>
+        <v>0.4551</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4409</v>
+        <v>-0.0001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.574</v>
+        <v>0.4553</v>
       </c>
       <c r="V20" t="n">
-        <v>1.7989</v>
+        <v>-0.2856</v>
       </c>
       <c r="W20" t="n">
-        <v>3.0266</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0911</v>
+        <v>-1.905</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9179</v>
+        <v>-1.6076</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1732</v>
+        <v>-0.2973</v>
       </c>
       <c r="G21" t="n">
         <v>0.2052</v>
@@ -2092,13 +2092,13 @@
         <v>0.9654</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2137</v>
+        <v>1.3998</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1928</v>
+        <v>0.5031</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0209</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6138</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. RAMOS BELASTEGUI</t>
+          <t>J. ORAMAS MARTEL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2085</v>
+        <v>-2.99</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4562</v>
+        <v>-2.7553</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7523</v>
+        <v>-0.2348</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5877</v>
+        <v>-2.7929</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1793</v>
+        <v>-1.0138</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4084</v>
+        <v>-1.7791</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2355</v>
+        <v>-2.0477</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6274</v>
+        <v>-0.6688</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6081</v>
+        <v>-1.379</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3522</v>
+        <v>-0.7451</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.345</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8003</v>
+        <v>-0.4002</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5792</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5792</v>
+        <v>0.1931</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0277</v>
+        <v>0.2895</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2207</v>
+        <v>-0.0278</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2484</v>
+        <v>0.3173</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2277</v>
+        <v>0.2856</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. ORAMAS MARTEL</t>
+          <t>E. RAMOS BELASTEGUI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4286</v>
+        <v>-3.1051</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.169</v>
+        <v>-1.3528</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2596</v>
+        <v>-1.7523</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.7929</v>
+        <v>-2.5877</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0138</v>
+        <v>-1.1793</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7791</v>
+        <v>-1.4084</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.0477</v>
+        <v>-1.2355</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6688</v>
+        <v>-0.6274</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.379</v>
+        <v>-0.6081</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7451</v>
+        <v>-1.3522</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.345</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4002</v>
+        <v>-0.8003</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7723</v>
+        <v>0.5792</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.149</v>
+        <v>0.1311</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4415</v>
+        <v>-0.1173</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2925</v>
+        <v>0.2484</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2856</v>
+        <v>-1.2277</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4143</v>
+        <v>-4.4017</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3733</v>
+        <v>-1.6836</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.041</v>
+        <v>-2.7182</v>
       </c>
       <c r="G24" t="n">
         <v>-3.181</v>
@@ -2326,13 +2326,13 @@
         <v>0.7723</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1874</v>
+        <v>0.2</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1928</v>
+        <v>-0.1174</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0054</v>
+        <v>0.3174</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2277</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>9.583099999999998</v>
+        <v>9.583299999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>9.218700000000002</v>
+        <v>9.218799999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3646000000000007</v>
+        <v>0.3647000000000005</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1038000000000001</v>
+        <v>0.1038000000000006</v>
       </c>
       <c r="H25" t="n">
         <v>2.760200000000002</v>
@@ -2404,13 +2404,13 @@
         <v>14.4808</v>
       </c>
       <c r="S25" t="n">
-        <v>10.6193</v>
+        <v>10.6194</v>
       </c>
       <c r="T25" t="n">
         <v>3.3068</v>
       </c>
       <c r="U25" t="n">
-        <v>7.3125</v>
+        <v>7.3127</v>
       </c>
       <c r="V25" t="n">
         <v>1.7563</v>
